--- a/data/out/best_models_ml/in/best_models_ml.xlsx
+++ b/data/out/best_models_ml/in/best_models_ml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\out\best_models_ml\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8A4A90-8F3F-4122-8660-657A4FE97B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BFB873-AFA3-4102-9EB3-1E40BBC1A95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/out/best_models_ml/in/best_models_ml.xlsx
+++ b/data/out/best_models_ml/in/best_models_ml.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\out\best_models_ml\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BFB873-AFA3-4102-9EB3-1E40BBC1A95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61007A5F-CF46-44A2-A5F2-E1E3465A56DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
   <si>
     <t>variant</t>
   </si>
@@ -222,39 +222,6 @@
   </si>
   <si>
     <t>{'name': 'v8_only_gen_no_solar_enso_lags', 'description': 'Only generation variables (except SOLAR) + ENSO + 24 lags of PRECIO', 'cols_dropped_missing': [], 'n_before': 48192, 'date_range_applied': None, 'cols_used': ['PRECIO', 'FECHA_HORA', 'TERMICA', 'HIDRAULICA', 'SOLAR', 'COGENERADOR', 'EOLICA', 'NIVEL_ENSO'], 'n_after': 48192, 'saved_variant_csv': '..\\..\\data\\out\\variants\\v8_only_gen_no_solar_enso_lags\\dataset_v8_only_gen_no_solar_enso_lags.csv'}</t>
-  </si>
-  <si>
-    <t>v9_date_range_all</t>
-  </si>
-  <si>
-    <t>Decision Tree</t>
-  </si>
-  <si>
-    <t>{'max_depth': 5, 'min_samples_split': 2}</t>
-  </si>
-  <si>
-    <t>{'name': 'v9_date_range_all', 'description': 'All variables, restricted to 2024-01-01 to 2025-06-30', 'cols_dropped_missing': [], 'n_before': 48192, 'date_range_applied': ('2024-01-01 00:00:00', '2025-06-30 00:00:00'), 'cols_used': ['FECHA_HORA', 'YEAR', 'MONTH', 'DAY', 'HORA', 'PRECIO', 'TERMICA', 'HIDRAULICA', 'SOLAR', 'COGENERADOR', 'EOLICA', 'NIVEL_ENSO', 'FUEL_CONS_ACPM', 'FUEL_CONS_CARBON', 'FUEL_CONS_COMBUSTOLEO', 'FUEL_CONS_CRUDO', 'FUEL_CONS_GAS', 'FUEL_CONS_GAS_NI', 'FUEL_CONS_GLP', 'FUEL_COST_CARBON', 'FUEL_COST_GAS', 'FUEL_COST_GAS_NI', 'FUEL_COST_COMBUSTOLEO', 'IPC_VAR_MOM_PCT', 'IPP_VAR_PN_MOM_PCT', 'IPP_VAR_OI_MOM_PCT', 'DIA_SEMANA', 'FESTIVO'], 'n_after': 13105, 'saved_variant_csv': '..\\..\\data\\out\\variants\\v9_date_range_all\\dataset_v9_date_range_all.csv'}</t>
-  </si>
-  <si>
-    <t>v9_date_range_all_lags</t>
-  </si>
-  <si>
-    <t>{'name': 'v9_date_range_all_lags', 'description': 'All variables, restricted to 2024-01-01 to 2025-06-30 + 24 lags of PRECIO', 'cols_dropped_missing': [], 'n_before': 48192, 'date_range_applied': ('2024-01-01 00:00:00', '2025-06-30 00:00:00'), 'cols_used': ['FECHA_HORA', 'YEAR', 'MONTH', 'DAY', 'HORA', 'PRECIO', 'TERMICA', 'HIDRAULICA', 'SOLAR', 'COGENERADOR', 'EOLICA', 'NIVEL_ENSO', 'FUEL_CONS_ACPM', 'FUEL_CONS_CARBON', 'FUEL_CONS_COMBUSTOLEO', 'FUEL_CONS_CRUDO', 'FUEL_CONS_GAS', 'FUEL_CONS_GAS_NI', 'FUEL_CONS_GLP', 'FUEL_COST_CARBON', 'FUEL_COST_GAS', 'FUEL_COST_GAS_NI', 'FUEL_COST_COMBUSTOLEO', 'IPC_VAR_MOM_PCT', 'IPP_VAR_PN_MOM_PCT', 'IPP_VAR_OI_MOM_PCT', 'DIA_SEMANA', 'FESTIVO', 'PRECIO_lag_1', 'PRECIO_lag_2', 'PRECIO_lag_3', 'PRECIO_lag_4', 'PRECIO_lag_5', 'PRECIO_lag_6', 'PRECIO_lag_7', 'PRECIO_lag_8', 'PRECIO_lag_9', 'PRECIO_lag_10', 'PRECIO_lag_11', 'PRECIO_lag_12', 'PRECIO_lag_13', 'PRECIO_lag_14', 'PRECIO_lag_15', 'PRECIO_lag_16', 'PRECIO_lag_17', 'PRECIO_lag_18', 'PRECIO_lag_19', 'PRECIO_lag_20', 'PRECIO_lag_21', 'PRECIO_lag_22', 'PRECIO_lag_23', 'PRECIO_lag_24'], 'n_after': 13081, 'saved_variant_csv': '..\\..\\data\\out\\variants\\v9_date_range_all_lags\\dataset_v9_date_range_all_lags.csv'}</t>
-  </si>
-  <si>
-    <t>v10_date_range_no_solar</t>
-  </si>
-  <si>
-    <t>{'max_depth': None, 'min_samples_split': 5}</t>
-  </si>
-  <si>
-    <t>{'name': 'v10_date_range_no_solar', 'description': 'All variables except SOLAR, restricted to 2024-01-01 to 2025-06-30', 'cols_dropped_missing': [], 'n_before': 48192, 'date_range_applied': ('2024-01-01 00:00:00', '2025-06-30 00:00:00'), 'cols_used': ['FECHA_HORA', 'YEAR', 'MONTH', 'DAY', 'HORA', 'PRECIO', 'TERMICA', 'HIDRAULICA', 'COGENERADOR', 'EOLICA', 'NIVEL_ENSO', 'FUEL_CONS_ACPM', 'FUEL_CONS_CARBON', 'FUEL_CONS_COMBUSTOLEO', 'FUEL_CONS_CRUDO', 'FUEL_CONS_GAS', 'FUEL_CONS_GAS_NI', 'FUEL_CONS_GLP', 'FUEL_COST_CARBON', 'FUEL_COST_GAS', 'FUEL_COST_GAS_NI', 'FUEL_COST_COMBUSTOLEO', 'IPC_VAR_MOM_PCT', 'IPP_VAR_PN_MOM_PCT', 'IPP_VAR_OI_MOM_PCT', 'DIA_SEMANA', 'FESTIVO'], 'n_after': 13105, 'saved_variant_csv': '..\\..\\data\\out\\variants\\v10_date_range_no_solar\\dataset_v10_date_range_no_solar.csv'}</t>
-  </si>
-  <si>
-    <t>v10_date_range_no_solar_lags</t>
-  </si>
-  <si>
-    <t>{'name': 'v10_date_range_no_solar_lags', 'description': 'All variables except SOLAR, restricted to 2024-01-01 to 2025-06-30 + 24 lags of PRECIO', 'cols_dropped_missing': [], 'n_before': 48192, 'date_range_applied': ('2024-01-01 00:00:00', '2025-06-30 00:00:00'), 'cols_used': ['FECHA_HORA', 'YEAR', 'MONTH', 'DAY', 'HORA', 'PRECIO', 'TERMICA', 'HIDRAULICA', 'COGENERADOR', 'EOLICA', 'NIVEL_ENSO', 'FUEL_CONS_ACPM', 'FUEL_CONS_CARBON', 'FUEL_CONS_COMBUSTOLEO', 'FUEL_CONS_CRUDO', 'FUEL_CONS_GAS', 'FUEL_CONS_GAS_NI', 'FUEL_CONS_GLP', 'FUEL_COST_CARBON', 'FUEL_COST_GAS', 'FUEL_COST_GAS_NI', 'FUEL_COST_COMBUSTOLEO', 'IPC_VAR_MOM_PCT', 'IPP_VAR_PN_MOM_PCT', 'IPP_VAR_OI_MOM_PCT', 'DIA_SEMANA', 'FESTIVO', 'PRECIO_lag_1', 'PRECIO_lag_2', 'PRECIO_lag_3', 'PRECIO_lag_4', 'PRECIO_lag_5', 'PRECIO_lag_6', 'PRECIO_lag_7', 'PRECIO_lag_8', 'PRECIO_lag_9', 'PRECIO_lag_10', 'PRECIO_lag_11', 'PRECIO_lag_12', 'PRECIO_lag_13', 'PRECIO_lag_14', 'PRECIO_lag_15', 'PRECIO_lag_16', 'PRECIO_lag_17', 'PRECIO_lag_18', 'PRECIO_lag_19', 'PRECIO_lag_20', 'PRECIO_lag_21', 'PRECIO_lag_22', 'PRECIO_lag_23', 'PRECIO_lag_24'], 'n_after': 13081, 'saved_variant_csv': '..\\..\\data\\out\\variants\\v10_date_range_no_solar_lags\\dataset_v10_date_range_no_solar_lags.csv'}</t>
   </si>
 </sst>
 </file>
@@ -273,6 +240,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -593,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="27.140625" customWidth="1"/>
@@ -1399,194 +1367,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18">
-        <v>-0.85947654167938836</v>
-      </c>
-      <c r="F18">
-        <v>100.63169829555849</v>
-      </c>
-      <c r="G18">
-        <v>18009.300976196169</v>
-      </c>
-      <c r="H18">
-        <v>134.19873686512909</v>
-      </c>
-      <c r="I18">
-        <v>80.800783963230273</v>
-      </c>
-      <c r="J18">
-        <v>13105</v>
-      </c>
-      <c r="K18">
-        <v>10484</v>
-      </c>
-      <c r="L18">
-        <v>2621</v>
-      </c>
-      <c r="M18">
-        <v>10.02586770057678</v>
-      </c>
-      <c r="N18" t="s">
-        <v>65</v>
-      </c>
-      <c r="O18">
-        <v>-515.08939908046329</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0.35415405462165522</v>
-      </c>
-      <c r="F19">
-        <v>25.854412334229931</v>
-      </c>
-      <c r="G19">
-        <v>6230.3244034377203</v>
-      </c>
-      <c r="H19">
-        <v>78.932404014053191</v>
-      </c>
-      <c r="I19">
-        <v>14.018933623135149</v>
-      </c>
-      <c r="J19">
-        <v>13081</v>
-      </c>
-      <c r="K19">
-        <v>10464</v>
-      </c>
-      <c r="L19">
-        <v>2617</v>
-      </c>
-      <c r="M19">
-        <v>1.798996210098267</v>
-      </c>
-      <c r="N19" t="s">
-        <v>67</v>
-      </c>
-      <c r="O19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20">
-        <v>-3.1105570269601319</v>
-      </c>
-      <c r="F20">
-        <v>121.0727797914282</v>
-      </c>
-      <c r="G20">
-        <v>39811.343149015687</v>
-      </c>
-      <c r="H20">
-        <v>199.52780044148159</v>
-      </c>
-      <c r="I20">
-        <v>97.666830453667714</v>
-      </c>
-      <c r="J20">
-        <v>13105</v>
-      </c>
-      <c r="K20">
-        <v>10484</v>
-      </c>
-      <c r="L20">
-        <v>2621</v>
-      </c>
-      <c r="M20">
-        <v>1.107896089553833</v>
-      </c>
-      <c r="N20" t="s">
-        <v>70</v>
-      </c>
-      <c r="O20">
-        <v>-518.94056899242105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0.3538570119011395</v>
-      </c>
-      <c r="F21">
-        <v>25.2679194497411</v>
-      </c>
-      <c r="G21">
-        <v>6233.1899049148687</v>
-      </c>
-      <c r="H21">
-        <v>78.950553544068768</v>
-      </c>
-      <c r="I21">
-        <v>13.546613027771761</v>
-      </c>
-      <c r="J21">
-        <v>13081</v>
-      </c>
-      <c r="K21">
-        <v>10464</v>
-      </c>
-      <c r="L21">
-        <v>2617</v>
-      </c>
-      <c r="M21">
-        <v>1.9178953170776369</v>
-      </c>
-      <c r="N21" t="s">
-        <v>72</v>
-      </c>
-      <c r="O21" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
